--- a/dataset_t6_grouped/results2/G2/G2_T3380_W0028F0001T0006Z000C1N85_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G2/G2_T3380_W0028F0001T0006Z000C1N85_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>48.75096195214029</v>
+        <v>7.922031317222798</v>
       </c>
       <c r="D2" t="n">
-        <v>48.71107579458192</v>
+        <v>7.915549816619562</v>
       </c>
       <c r="E2" t="n">
-        <v>21.64637570269823</v>
+        <v>3.517536051688462</v>
       </c>
       <c r="F2" t="n">
-        <v>21.69352845134862</v>
+        <v>3.525198373344151</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>24.06499889486073</v>
+        <v>3.910562320414869</v>
       </c>
       <c r="D3" t="n">
-        <v>24.23466577330633</v>
+        <v>3.938133188162278</v>
       </c>
       <c r="E3" t="n">
-        <v>21.64637570269823</v>
+        <v>3.517536051688462</v>
       </c>
       <c r="F3" t="n">
-        <v>21.69352845134862</v>
+        <v>3.525198373344151</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>33.4237696546605</v>
+        <v>5.431362568882332</v>
       </c>
       <c r="D4" t="n">
-        <v>33.0657344173445</v>
+        <v>5.373181842818481</v>
       </c>
       <c r="E4" t="n">
-        <v>21.64637570269823</v>
+        <v>3.517536051688462</v>
       </c>
       <c r="F4" t="n">
-        <v>21.69352845134862</v>
+        <v>3.525198373344151</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>81.07324684325383</v>
+        <v>13.17440261202875</v>
       </c>
       <c r="D5" t="n">
-        <v>81.16510254995897</v>
+        <v>13.18932916436833</v>
       </c>
       <c r="E5" t="n">
-        <v>21.64637570269823</v>
+        <v>3.517536051688462</v>
       </c>
       <c r="F5" t="n">
-        <v>21.69352845134862</v>
+        <v>3.525198373344151</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
